--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/create-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/create-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
   <si>
     <t>Statement: WorkoutSessionRepository.create(data, exercises) – atomically creates session.</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Valid data, 1 exercise</t>
   </si>
   <si>
-    <t>Returns session with 1 exercise</t>
+    <t>Returns session</t>
   </si>
   <si>
     <t>Passed</t>
@@ -124,9 +124,6 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Returns session with all</t>
-  </si>
-  <si>
     <t>EC-3</t>
   </si>
   <si>
@@ -166,7 +163,10 @@
     <t>memberId = ""</t>
   </si>
   <si>
-    <t>memberId = "a"</t>
+    <t>memberId = "a" (inex)</t>
+  </si>
+  <si>
+    <t>memberId = "a" (exist)</t>
   </si>
   <si>
     <t>Exercises length</t>
@@ -184,16 +184,10 @@
     <t>BVA-1 EmptyID</t>
   </si>
   <si>
-    <t>BVA-2 OneCharID</t>
-  </si>
-  <si>
-    <t>BVA-3 ZeroLen</t>
-  </si>
-  <si>
-    <t>BVA-4 OneLen</t>
-  </si>
-  <si>
-    <t>Persists successfully</t>
+    <t>BVA-2 InexCharID</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistCharID</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -205,15 +199,9 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Returns session</t>
-  </si>
-  <si>
     <t>2 exercises provided</t>
   </si>
   <si>
-    <t>Returns session with 2</t>
-  </si>
-  <si>
     <t>exercises = []</t>
   </si>
   <si>
@@ -233,6 +221,9 @@
   </si>
   <si>
     <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
   </si>
   <si>
     <t>1 exercise</t>
@@ -976,7 +967,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>33</v>
@@ -987,13 +978,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -1004,13 +995,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>33</v>
@@ -1021,13 +1012,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>33</v>
@@ -1041,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1051,13 +1042,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1065,10 +1056,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1087,10 +1078,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1098,9 +1089,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1112,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1147,10 +1149,10 @@
         <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>33</v>
@@ -1164,10 +1166,10 @@
         <v>55</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>33</v>
@@ -1181,29 +1183,12 @@
         <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1215,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1231,10 +1216,10 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>27</v>
@@ -1251,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -1260,7 +1245,7 @@
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>33</v>
@@ -1277,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
@@ -1291,16 +1276,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
@@ -1311,16 +1296,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -1331,16 +1316,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -1354,13 +1339,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -1374,13 +1359,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
@@ -1394,13 +1379,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>33</v>
@@ -1414,15 +1399,35 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1451,16 +1456,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1468,45 +1473,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1515,19 +1520,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/create-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/create-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
-  <si>
-    <t>Statement: WorkoutSessionRepository.create(data, exercises) – atomically creates session.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="83">
+  <si>
+    <t>Statement: WorkoutSessionRepository.create(data, exercises) – Creates a new workout session with its associated exercises. Returns the created WorkoutSessionWithExercises on success. Throws WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.") if the exercises array is empty. Throws NotFoundError("Member not found") if no member exists with the given memberId. Throws TransactionError if the database write fails.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible | exercises.length &gt;= 1</t>
+    <t>Database is accessible. A member with the given memberId may or may not exist. The exercises array may be empty or contain one or more items.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt; | throws Error</t>
+    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Persists records or throws Error.</t>
+    <t>On success: WorkoutSessionWithExercises returned with result.id: SESSION_ID, result.exercises.length matching the number of provided exercises, and result.exercises[0].exerciseId matching the first exercise input. On failure: WorkoutSessionRequiresExercisesError, NotFoundError, or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,34 +64,34 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Exercises list</t>
-  </si>
-  <si>
-    <t>Length &gt;= 1</t>
-  </si>
-  <si>
-    <t>Multiple exercises</t>
-  </si>
-  <si>
-    <t>Length = 0 (RequiresExercisesError)</t>
+    <t>Exercise count</t>
+  </si>
+  <si>
+    <t>One exercise provided → WorkoutSessionWithExercises returned with result.exercises.length: 1, result.exercises[0].exerciseId: EXERCISE_ID</t>
+  </si>
+  <si>
+    <t>Multiple exercises provided → WorkoutSessionWithExercises returned with result.exercises.length: 2, result.exercises[1].exerciseId: "exercise-uuid-002"</t>
+  </si>
+  <si>
+    <t>Empty exercises array → WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.")</t>
   </si>
   <si>
     <t>Member existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Database status</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Failure (TransactionError)</t>
+    <t>Member exists → WorkoutSessionWithExercises returned</t>
+  </si>
+  <si>
+    <t>No member with given memberId → NotFoundError("Member not found")</t>
+  </si>
+  <si>
+    <t>Database write</t>
+  </si>
+  <si>
+    <t>Write succeeds → WorkoutSessionWithExercises returned</t>
+  </si>
+  <si>
+    <t>Write fails → TransactionError("DB error")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -112,10 +112,10 @@
     <t>EC-1, EC-4, EC-6</t>
   </si>
   <si>
-    <t>Valid data, 1 exercise</t>
-  </si>
-  <si>
-    <t>Returns session</t>
+    <t>data: CREATE_SESSION_INPUT, exercises: EXERCISE_INPUT (1 item, member exists, write succeeds)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result equal to MOCK_SESSION_WITH_EXERCISES, result.id: SESSION_ID, result.exercises.length: 1, result.exercises[0].exerciseId: EXERCISE_ID</t>
   </si>
   <si>
     <t>Passed</t>
@@ -124,31 +124,37 @@
     <t>EC-2</t>
   </si>
   <si>
+    <t>data: CREATE_SESSION_INPUT, exercises: [EXERCISE_INPUT[0], { exerciseId: "exercise-uuid-002", sets: 4, reps: 8, weight: 60.0 }] (member exists, write succeeds)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.exercises.length: 2, result.exercises[1].exerciseId: "exercise-uuid-002", result.exercises[1].sets: 4</t>
+  </si>
+  <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Empty exercises array</t>
-  </si>
-  <si>
-    <t>Throws RequiresExercisesError</t>
+    <t>data: CREATE_SESSION_INPUT, exercises: [] (empty array)</t>
+  </si>
+  <si>
+    <t>throws WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.")</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Member not found</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>data: CREATE_SESSION_INPUT, exercises: EXERCISE_INPUT (no member with given memberId)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Member not found")</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>DB write failure</t>
-  </si>
-  <si>
-    <t>Throws TransactionError</t>
+    <t>data: CREATE_SESSION_INPUT, exercises: EXERCISE_INPUT (member exists, database write fails with "DB error")</t>
+  </si>
+  <si>
+    <t>throws TransactionError("DB error")</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -157,37 +163,55 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>MemberId length</t>
-  </si>
-  <si>
-    <t>memberId = ""</t>
-  </si>
-  <si>
-    <t>memberId = "a" (inex)</t>
-  </si>
-  <si>
-    <t>memberId = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Exercises length</t>
-  </si>
-  <si>
-    <t>length = 0</t>
-  </si>
-  <si>
-    <t>length = 1</t>
+    <t>memberId length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>exercises length</t>
+  </si>
+  <si>
+    <t>length: 0 (empty array), length: 1 (one item)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 InexCharID</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistCharID</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>data: { ...CREATE_SESSION_INPUT, memberId: "" } (no member with that ID), exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>data: { ...CREATE_SESSION_INPUT, memberId: "a" } (no member with that ID), exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>data: { ...CREATE_SESSION_INPUT, memberId: "a" } (member exists with id: "a"), exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.memberId: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (l=0)</t>
+  </si>
+  <si>
+    <t>throws WorkoutSessionRequiresExercisesError</t>
+  </si>
+  <si>
+    <t>BVA-2 (l=1)</t>
+  </si>
+  <si>
+    <t>data: CREATE_SESSION_INPUT, exercises: [{ exerciseId: EXERCISE_ID, sets: 3, reps: 10, weight: 80.0 }] (member exists)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.exercises.length: 1, result.exercises[0].exerciseId: EXERCISE_ID</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -196,39 +220,12 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>2 exercises provided</t>
-  </si>
-  <si>
-    <t>exercises = []</t>
-  </si>
-  <si>
-    <t>Invalid memberId</t>
-  </si>
-  <si>
-    <t>Database exception</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>1 exercise</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -259,7 +256,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-01/WSM-02/WSM-03/WSM-04</t>
+    <t>REPO-19</t>
   </si>
   <si>
     <t>n/a</t>
@@ -825,7 +822,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>17</v>
@@ -839,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -867,7 +864,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
@@ -895,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
@@ -964,10 +961,10 @@
         <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>33</v>
@@ -978,13 +975,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -995,13 +992,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>33</v>
@@ -1012,13 +1009,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>33</v>
@@ -1032,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1042,13 +1039,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1056,10 +1053,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1067,43 +1064,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1129,7 +1093,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>27</v>
@@ -1146,13 +1110,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>33</v>
@@ -1163,13 +1127,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>33</v>
@@ -1183,12 +1147,46 @@
         <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1216,10 +1214,10 @@
         <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>27</v>
@@ -1236,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -1262,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>33</v>
@@ -1276,16 +1274,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>33</v>
@@ -1296,16 +1294,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>33</v>
@@ -1316,16 +1314,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>33</v>
@@ -1339,13 +1337,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>33</v>
@@ -1359,13 +1357,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>33</v>
@@ -1379,13 +1377,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>33</v>
@@ -1399,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>33</v>
@@ -1422,10 +1420,10 @@
         <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>33</v>
@@ -1456,16 +1454,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1473,39 +1471,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1">
         <v>10</v>
@@ -1520,19 +1518,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
